--- a/output/pdf_financials_xlsx/VLTA.xlsx
+++ b/output/pdf_financials_xlsx/VLTA.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.006212</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.008527</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.004919</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.879465</v>
+        <v>-2.885677</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.077701</v>
+        <v>-1.086228</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.537957</v>
+        <v>-1.542876</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.870367</v>
+        <v>-2.876579</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.062241</v>
+        <v>-1.070768</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.520881</v>
+        <v>-1.5258</v>
       </c>
     </row>
     <row r="30">
@@ -982,7 +982,7 @@
         <v>0.051582</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>3.033063</v>
       </c>
     </row>
     <row r="35">
@@ -1014,7 +1014,7 @@
         <v>0.051582</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>3.033063</v>
       </c>
     </row>
     <row r="37">
@@ -1206,7 +1206,7 @@
         <v>0.012004</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.226585</v>
+        <v>0.193522</v>
       </c>
     </row>
     <row r="49">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">

--- a/output/pdf_financials_xlsx/VLTA.xlsx
+++ b/output/pdf_financials_xlsx/VLTA.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.344342</v>
+        <v>0.455452</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.395117</v>
+        <v>0.517065</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.499057</v>
+        <v>0.555464</v>
       </c>
     </row>
     <row r="8">
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.06823700000000001</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.017168</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.06823700000000001</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.017168</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.612389</v>
+        <v>-1.680626</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.491664</v>
+        <v>-0.508832</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-1.327179</v>
@@ -3734,7 +3734,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>-0.06823700000000001</v>
       </c>
@@ -4329,7 +4333,11 @@
           <t>Common shares issued in private placement 13,920,000 599,600 96,400</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -4552,7 +4560,11 @@
           <t>Common shares issued in private placement 21,701,950 1,272,032 66,303</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -5519,7 +5531,11 @@
           <t>Directors’ fees 10</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -6075,7 +6091,11 @@
           <t>Directors’ fees 11</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E110" s="5" t="n">
         <v>0.11111</v>
       </c>
